--- a/data/dividends_info_20260510.xlsx
+++ b/data/dividends_info_20260510.xlsx
@@ -9832,7 +9832,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -10104,7 +10104,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -10189,7 +10189,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -10216,14 +10216,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10240,7 +10240,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -10257,7 +10257,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -10267,14 +10267,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -10284,14 +10284,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -10308,7 +10308,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -10318,14 +10318,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10342,7 +10342,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10352,14 +10352,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10369,14 +10369,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10393,7 +10393,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10410,7 +10410,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10420,14 +10420,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10437,14 +10437,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10461,7 +10461,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10471,14 +10471,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10488,14 +10488,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10529,7 +10529,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10546,7 +10546,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10556,14 +10556,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10580,7 +10580,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10590,14 +10590,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10614,7 +10614,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10631,7 +10631,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10641,14 +10641,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10665,7 +10665,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10675,14 +10675,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10716,7 +10716,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10818,7 +10818,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10869,7 +10869,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10937,7 +10937,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10954,7 +10954,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10971,7 +10971,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10988,7 +10988,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10998,14 +10998,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -11056,7 +11056,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11124,7 +11124,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11141,7 +11141,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11158,7 +11158,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11168,14 +11168,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11185,14 +11185,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11226,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11243,7 +11243,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11253,14 +11253,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11270,14 +11270,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11287,14 +11287,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11304,14 +11304,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -11338,14 +11338,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11355,14 +11355,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11379,7 +11379,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11396,7 +11396,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11413,7 +11413,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11447,7 +11447,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11457,14 +11457,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11474,14 +11474,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -11549,7 +11549,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11559,14 +11559,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11583,7 +11583,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11593,14 +11593,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11634,7 +11634,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11651,7 +11651,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -11821,7 +11821,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -11855,7 +11855,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11865,14 +11865,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11882,14 +11882,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11899,14 +11899,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11916,14 +11916,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11933,14 +11933,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11950,14 +11950,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11967,14 +11967,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -12008,7 +12008,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12018,14 +12018,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12059,7 +12059,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12069,14 +12069,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -12110,7 +12110,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12161,7 +12161,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12178,7 +12178,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12212,7 +12212,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12297,7 +12297,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12314,7 +12314,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>TALEA GROUP</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12331,7 +12331,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>TALEA GROUP</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12382,7 +12382,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12392,14 +12392,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12409,14 +12409,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12426,14 +12426,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12443,14 +12443,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12460,14 +12460,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12484,7 +12484,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12501,7 +12501,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12511,14 +12511,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12535,7 +12535,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12545,14 +12545,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12569,7 +12569,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12579,14 +12579,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12596,14 +12596,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12620,7 +12620,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12637,7 +12637,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12647,7 +12647,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -12688,7 +12688,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12705,7 +12705,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12715,14 +12715,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12732,14 +12732,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12756,7 +12756,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12773,7 +12773,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12783,14 +12783,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12807,7 +12807,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12817,14 +12817,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12841,7 +12841,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12851,14 +12851,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12875,7 +12875,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12892,7 +12892,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12909,7 +12909,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12926,7 +12926,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12943,7 +12943,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12953,14 +12953,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12970,14 +12970,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -13113,7 +13113,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -13130,7 +13130,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -13147,7 +13147,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -13164,7 +13164,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -13198,7 +13198,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Homizy SIIQ S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -13208,14 +13208,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -13232,7 +13232,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Homizy SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13242,7 +13242,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -13270,95 +13270,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Homizy SIIQ S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>KME Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TRAWELL CO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>